--- a/templates/mau_danh_sach_lop.xlsx
+++ b/templates/mau_danh_sach_lop.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MXV2504\AppData\Roaming\Claude\scratch-workspaces\dad96b1b-ba62-4286-94bf-d7bcacf9ea42\edcc0e3f-4cbe-4a56-ad5a-0df56f10fe41\scratch-2026-10-29-175100\frontend\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MXV2504\OneDrive - Sở GDĐT Nam Định\Tài liệu\GIAOTIENSMART\frontend\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{16A3601A-1D4A-4755-98B6-8581699E7BD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D46251F-743A-4396-8560-FAD5E6958EE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13245" xr2:uid="{825800BC-0B82-4A60-9FC0-6E595FC5FE06}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>STT</t>
   </si>
@@ -90,6 +90,15 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>Nhóm thi đua</t>
+  </si>
+  <si>
+    <t>Lớp chọn</t>
+  </si>
+  <si>
+    <t>Đại trà</t>
   </si>
 </sst>
 </file>
@@ -478,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66324B06-617C-484B-B5DE-27499EEA845B}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.125" bestFit="1" customWidth="1"/>
@@ -487,9 +496,10 @@
     <col min="4" max="4" width="6.125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.1875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.3125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="13.9" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="13.9" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -508,8 +518,11 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="2" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -528,8 +541,11 @@
       <c r="F2" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="G2" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -547,6 +563,9 @@
       </c>
       <c r="F3" s="1" t="s">
         <v>16</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
